--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-11.17</v>
+        <v>-15.74</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,32 +1182,32 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,67 +1450,67 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-17.52</v>
+        <v>-11.17</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,32 +1613,32 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1886,64 +1886,64 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1971,31 +1971,31 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-13.1</v>
+        <v>-17.52</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2044,17 +2044,17 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2312,37 +2312,37 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2357,17 +2357,17 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,22 +2392,22 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -2417,16 +2417,16 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-6.33</v>
+        <v>-13.1</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2743,62 +2743,62 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-5.75</v>
+        <v>-6.33</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3174,69 +3174,69 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-104.62</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>146.46</t>
+          <t>148.52</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-7.07</v>
+        <v>-5.75</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,32 +3337,32 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3605,42 +3605,42 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3650,22 +3650,22 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-115.09</t>
+          <t>-72.00</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>145.46</t>
+          <t>146.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-9.17864632394204</t>
+          <t>-8.854520802377994</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-13.85</v>
+        <v>-7.07</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,32 +3768,32 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4036,27 +4036,27 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-180.42</t>
+          <t>-115.09</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.40</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4131,26 +4131,26 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>128.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.328919899724902</t>
+          <t>-9.17864632394204</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-9.76</v>
+        <v>-13.85</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4467,67 +4467,67 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-365.46</t>
+          <t>-180.42</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.32</t>
+          <t>-102.40</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>152.4</t>
+          <t>122.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>126.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>144.94</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.069111351122272</t>
+          <t>-8.328919899724902</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4.52</v>
+        <v>-9.76</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,32 +4630,32 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4903,180 +4903,180 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>18.51</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>19.13</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>19.07</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>19.14</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-365.46</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-101.32</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>1760.801928783383</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>205.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>152.4</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>127.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>144.94</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-8.069111351122272</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-5.28</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>18.67</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>19.18</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>19.17</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-3273.41</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-100.11</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>1763.369242199109</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>127.4</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>111.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>144.72</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-8.713550965896541</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-11.57</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-3.17</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>14.57</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5374,22 +5374,22 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-361.29</t>
+          <t>-3273.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-99.18</t>
+          <t>-100.11</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1763.369242199109</t>
+          <t>1760.801928783383</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>185.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>125.6</t>
+          <t>127.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>145.86</t>
+          <t>144.72</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.194977207752418</t>
+          <t>-8.713550965896541</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-9.529999999999999</v>
+        <v>-11.57</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>62.73145418091756</t>
+          <t>-4.914704939634603</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>63.74532724144069</t>
+          <t>3.89524476612966</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2.860984998026056</t>
+          <t>0.4035023817520423</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>274</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-15.74</v>
+        <v>-5.5</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,32 +1445,32 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-11.17</v>
+        <v>-15.74</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-17.52</v>
+        <v>-11.17</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,64 +2317,64 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2402,31 +2402,31 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-13.1</v>
+        <v>-17.52</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,42 +2738,42 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2788,17 +2788,17 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -2848,16 +2848,16 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-6.33</v>
+        <v>-13.1</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,67 +3169,67 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-5.75</v>
+        <v>-6.33</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,126 +3600,126 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>73.68</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>58.31</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-104.62</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>1758.628888888889</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>148.52</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>63.16</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>43.43</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-3.64</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-104.12</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>1760.801928783383</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>183.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>122.2</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>123.9</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>146.46</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-7.07</v>
+        <v>-5.75</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,47 +4031,47 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4081,22 +4081,22 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-115.09</t>
+          <t>-72.00</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>145.46</t>
+          <t>146.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-9.17864632394204</t>
+          <t>-8.854520802377994</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-13.85</v>
+        <v>-7.07</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,37 +4497,37 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-180.42</t>
+          <t>-115.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.40</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4562,26 +4562,26 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>128.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.328919899724902</t>
+          <t>-9.17864632394204</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-9.76</v>
+        <v>-13.85</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-365.46</t>
+          <t>-180.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.32</t>
+          <t>-102.40</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>152.4</t>
+          <t>122.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>126.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>144.94</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.069111351122272</t>
+          <t>-8.328919899724902</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4.52</v>
+        <v>-9.76</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-3273.41</t>
+          <t>-365.46</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.11</t>
+          <t>-101.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1760.801928783383</t>
+          <t>1758.628888888889</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>205.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>127.4</t>
+          <t>152.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>144.72</t>
+          <t>144.94</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.713550965896541</t>
+          <t>-8.069111351122272</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-11.57</v>
+        <v>-4.52</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-5.5</v>
+        <v>-7.5</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-15.74</v>
+        <v>-5.5</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,37 +1871,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-11.17</v>
+        <v>-15.74</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-17.52</v>
+        <v>-11.17</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,64 +2748,64 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2833,31 +2833,31 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-13.1</v>
+        <v>-17.52</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,47 +3164,47 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3219,17 +3219,17 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,22 +3254,22 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -3279,16 +3279,16 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-6.33</v>
+        <v>-13.1</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,72 +3595,72 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-5.75</v>
+        <v>-6.33</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,79 +4026,79 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-104.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>146.46</t>
+          <t>148.52</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-7.07</v>
+        <v>-5.75</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,52 +4457,52 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4512,22 +4512,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-115.09</t>
+          <t>-72.00</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>145.46</t>
+          <t>146.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-9.17864632394204</t>
+          <t>-8.854520802377994</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-13.85</v>
+        <v>-7.07</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,37 +4888,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,37 +4928,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-180.42</t>
+          <t>-115.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.40</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -4993,26 +4993,26 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>128.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.328919899724902</t>
+          <t>-9.17864632394204</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-9.76</v>
+        <v>-13.85</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-365.46</t>
+          <t>-180.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.32</t>
+          <t>-102.40</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1758.628888888889</t>
+          <t>1756.187130177515</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>205.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>152.4</t>
+          <t>122.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>126.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>144.94</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.069111351122272</t>
+          <t>-8.328919899724902</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-4.52</v>
+        <v>-9.76</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>265</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>18.99</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>149.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-7.5</v>
+        <v>-4.58</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-5.5</v>
+        <v>-7.5</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-15.74</v>
+        <v>-5.5</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,32 +2307,32 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-11.17</v>
+        <v>-15.74</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-17.52</v>
+        <v>-11.17</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,64 +3179,64 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3264,31 +3264,31 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-13.1</v>
+        <v>-17.52</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,42 +3600,42 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -3710,16 +3710,16 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-6.33</v>
+        <v>-13.1</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-5.75</v>
+        <v>-6.33</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,74 +4462,74 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-104.62</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>146.46</t>
+          <t>148.52</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-7.07</v>
+        <v>-5.75</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,47 +4893,47 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4943,22 +4943,22 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-115.09</t>
+          <t>-72.00</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>145.46</t>
+          <t>146.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-9.17864632394204</t>
+          <t>-8.854520802377994</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-13.85</v>
+        <v>-7.07</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,32 +5324,32 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5359,37 +5359,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-180.42</t>
+          <t>-115.09</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.40</t>
+          <t>-103.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1756.187130177515</t>
+          <t>1753.874446085672</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5424,26 +5424,26 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>128.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.46</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.328919899724902</t>
+          <t>-9.17864632394204</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-9.76</v>
+        <v>-13.85</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>256</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,288 +1014,293 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-47.71</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-107.24</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>1751.798672566372</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>129.6</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>109.4</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>153.1</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-6.82908030781107</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>5.373577389639848</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>231</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-59.68</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-106.38</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>1753.874446085672</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>104.6</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-9.047745343711238</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-4.58</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-8.71</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-6.33</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>17.9</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>18.99</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>149.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-9.047745343711238</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-4.582369281680613</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>127</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-5.28</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-8.71</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>17.9</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-9.85963190044408</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-7.498637052078394</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>72</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-8.71</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-5.28</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>17.95</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-15.74</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-10.28890369105602</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-5.504068257929575</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>196</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-2.11</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-8.71</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>18.55</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,37 +2758,37 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2773,12 +2798,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2793,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-11.17</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-11.15887376980629</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-15.74382468564805</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>22</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-0.79</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-2.11</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-17.52</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-10.32524633056233</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-11.1669115579013</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>146</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,7 +3499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3574,7 +3609,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3595,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,64 +3645,64 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,7 +3720,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3695,188 +3730,193 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-10.17221628922797</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-17.51536024833804</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>26</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2.28</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,47 +4066,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4081,17 +4121,17 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,22 +4156,22 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -4141,173 +4181,178 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-6.33</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-8.837099205753413</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-13.10188122580702</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>26</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-0.79</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,72 +4502,72 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-8.061684293016393</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-6.328986864126762</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>113</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-1.58</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
         <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,79 +4938,79 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-104.62</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>146.46</t>
+          <t>148.52</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-7.07</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-8.376720189178144</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-5.748816816578966</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>135</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-2.11</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,52 +5374,52 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>43.43</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5374,22 +5429,22 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-115.09</t>
+          <t>-72.00</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1753.874446085672</t>
+          <t>1751.798672566372</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>145.46</t>
+          <t>146.46</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-9.17864632394204</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-13.85</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-8.854520802377994</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-7.071830433775744</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>183</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-3.17</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-2.11</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,14 +1014,14 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF2" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>129.6</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,147 +1450,147 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-47.71</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-107.24</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>1749.258468335788</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>129.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>109.4</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>153.1</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-6.82908030781107</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>5.373577389639848</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>231</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-59.68</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-106.38</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>1751.798672566372</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>104.6</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-9.047745343711238</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-4.582369281680613</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>127</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG3" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>18.99</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>149.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,37 +3194,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -4066,14 +4066,14 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF9" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -4081,64 +4081,64 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-13.10188122580702</t>
+          <t>-17.51536024833804</t>
         </is>
       </c>
       <c r="BD9" t="n">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,47 +4502,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4557,17 +4557,17 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,22 +4592,22 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -4617,21 +4617,21 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-6.328986864126762</t>
+          <t>-13.10188122580702</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,102 +4832,102 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>-5.92</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.23</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-15.45</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>-5.07</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,72 +4938,72 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-5.748816816578966</t>
+          <t>-6.328986864126762</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,79 +5374,79 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>58.31</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>18.38</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>19.04</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-43.17</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>19.09</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-72.00</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-104.62</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1751.798672566372</t>
+          <t>1749.258468335788</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>146.46</t>
+          <t>148.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.854520802377994</t>
+          <t>-8.376720189178144</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-7.071830433775744</t>
+          <t>-5.748816816578966</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1029,132 +1029,132 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>1746.727941176471</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>152.68</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>1749.258468335788</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG2" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>129.6</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,7 +1886,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1896,137 +1896,137 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-47.71</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-107.24</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1746.727941176471</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>129.6</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>109.4</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>153.1</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-6.82908030781107</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>5.373577389639848</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>231</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-59.68</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-106.38</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1749.258468335788</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>104.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-9.047745343711238</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-4.582369281680613</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>127</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG4" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,7 +2322,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2332,67 +2332,67 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>18.99</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>149.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,7 +2758,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2768,67 +2768,67 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,7 +3194,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3204,67 +3204,67 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,7 +3630,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3640,27 +3640,27 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3670,12 +3670,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,7 +4066,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4076,67 +4076,67 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4502,7 +4502,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4517,64 +4517,64 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -4602,32 +4602,32 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-13.10188122580702</t>
+          <t>-17.51536024833804</t>
         </is>
       </c>
       <c r="BD10" t="n">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,7 +4938,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4948,37 +4948,37 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,22 +5028,22 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -5053,21 +5053,21 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-6.328986864126762</t>
+          <t>-13.10188122580702</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,102 +5268,102 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>-5.92</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-15.45</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>-5.07</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.23</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,7 +5374,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5384,62 +5384,62 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>75.44</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-43.17</t>
+          <t>-19.28</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.62</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1749.258468335788</t>
+          <t>1746.727941176471</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>111.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>148.52</t>
+          <t>149.84</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.376720189178144</t>
+          <t>-8.061684293016393</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-5.748816816578966</t>
+          <t>-6.328986864126762</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.32</t>
+          <t>18.24</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>152.68</t>
+          <t>150.4</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,132 +1465,132 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>18.32</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>1744.76872246696</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>152.68</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>1746.727941176471</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG3" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>129.6</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,147 +2322,147 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-47.71</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-107.24</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>1744.76872246696</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>129.6</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>109.4</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>153.1</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-6.82908030781107</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>5.373577389639848</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>231</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-59.68</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-106.38</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>1746.727941176471</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>104.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-9.047745343711238</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-4.582369281680613</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>127</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>18.99</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>149.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>19.01</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>147.56</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>145.88</t>
+          <t>147.56</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>149.38</t>
+          <t>145.88</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>148.46</t>
+          <t>149.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,64 +4953,64 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>17.86</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -5038,32 +5038,32 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>149.84</t>
+          <t>148.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-13.10188122580702</t>
+          <t>-17.51536024833804</t>
         </is>
       </c>
       <c r="BD11" t="n">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,47 +5374,47 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -5429,17 +5429,17 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-19.28</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-104.82</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1746.727941176471</t>
+          <t>1744.76872246696</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -5489,21 +5489,21 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.061684293016393</t>
+          <t>-8.837099205753413</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-6.328986864126762</t>
+          <t>-13.10188122580702</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>17.53</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>18.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>18.83</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18.83</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>275.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>134</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>113.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>150.4</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>150.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>5.094059701290561</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>275</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>275.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>17.7</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>18.87</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>19.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>93.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>93.40000000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>88.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>152.68</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>152.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9.995558126169087</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>19</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>17.61</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18.9</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>18.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>128.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>97.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>152.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-3.766599375176838</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>18</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>17.77</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>18.43</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>18.93</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>18.93</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>231.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>129.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>129.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>109.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>153.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>153.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>5.373577389639848</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>231</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>17.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>18.52</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>127.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>112.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>104.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>149.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-4.582369281680613</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>127</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>18.31</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>18.99</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>92.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>97.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>147.2</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>147.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-7.498637052078394</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>72</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>18.51</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>19.01</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>196.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>83.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>97.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>147.56</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>147.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-5.504068257929575</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>196</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,21 +4067,17 @@
           <t>18.81</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AM9" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP9" t="inlineStr">
         <is>
           <t>12.53</t>
@@ -4164,20 +4118,16 @@
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>98.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>145.88</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>145.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-15.74382468564805</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>22</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,21 +4497,17 @@
           <t>18.83</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AM10" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP10" t="inlineStr">
         <is>
           <t>21.95</t>
@@ -4600,20 +4548,16 @@
           <t>146.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>89.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>105.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>149.38</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>149.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-11.1669115579013</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>146</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>18.78</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>96.59999999999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>109.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>148.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>148.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-17.51536024833804</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>26</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>18.66</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>103.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>103.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>112.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>149.84</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>149.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-13.10188122580702</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>26</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1874,14 +1874,14 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -1889,126 +1889,126 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1742.24780058651</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1744.76872246696</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG4" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,14 +2304,14 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.86</v>
+        <v>18.74</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.04</v>
+        <v>19.01</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>66.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>145.88</v>
+        <v>147.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,37 +4454,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4494,11 +4494,11 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.92</v>
+        <v>18.86</v>
       </c>
       <c r="AN10" t="n">
         <v>19.04</v>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>89.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>149.38</v>
+        <v>145.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.96</v>
+        <v>18.92</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.03</v>
+        <v>19.04</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>96.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>148.46</v>
+        <v>149.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-9.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-11.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -5314,14 +5314,14 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AF12" t="inlineStr">
         <is>
           <t>100.0</t>
@@ -5329,60 +5329,60 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.98</v>
+        <v>18.96</v>
       </c>
       <c r="AN12" t="n">
         <v>19.03</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>3.17</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.82</t>
+          <t>-104.61</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1744.76872246696</t>
+          <t>1742.24780058651</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -5409,29 +5409,29 @@
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>103.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>109.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>149.84</v>
+        <v>148.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8.837099205753413</t>
+          <t>-10.17221628922797</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-13.10188122580702</t>
+          <t>-17.51536024833804</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>255</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,126 +2319,126 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>1740.191068814056</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>1742.24780058651</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.86</v>
+        <v>18.74</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.04</v>
+        <v>19.01</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>66.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>145.88</v>
+        <v>147.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,37 +4884,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4924,11 +4924,11 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.92</v>
+        <v>18.86</v>
       </c>
       <c r="AN11" t="n">
         <v>19.04</v>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>89.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>149.38</v>
+        <v>145.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.86</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.96</v>
+        <v>18.92</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.03</v>
+        <v>19.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.61</t>
+          <t>-104.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1742.24780058651</t>
+          <t>1740.191068814056</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>96.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>109.6</t>
+          <t>105.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>148.46</v>
+        <v>149.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-10.17221628922797</t>
+          <t>-10.32524633056233</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-17.51536024833804</t>
+          <t>-11.1669115579013</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3.260200344702716</t>
+          <t>-2.522084938000019</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>5.634721361463207</t>
+          <t>1.537549798864816</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,126 +2749,126 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>1737.831140350877</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>1740.191068814056</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG6" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.86</v>
+        <v>18.74</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.04</v>
+        <v>19.01</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>66.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>145.88</v>
+        <v>147.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-12.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-32.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,37 +5314,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5354,11 +5354,11 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.92</v>
+        <v>18.86</v>
       </c>
       <c r="AN12" t="n">
         <v>19.04</v>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.37</t>
+          <t>-104.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1740.191068814056</t>
+          <t>1737.831140350877</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>89.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>105.7</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>149.38</v>
+        <v>145.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-31</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-10.32524633056233</t>
+          <t>-11.15887376980629</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-11.1669115579013</t>
+          <t>-15.74382468564805</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>244</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,63 +1024,63 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1109,29 +1109,29 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2.522084938000019</t>
+          <t>-2.344673261373195</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1.537549798864816</t>
+          <t>-1.368909039925668</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3.260200344702716</t>
+          <t>-2.522084938000019</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5.634721361463207</t>
+          <t>1.537549798864816</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3179,126 +3179,126 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>1735.478102189781</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>1737.831140350877</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG7" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4034,63 +4034,63 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.79</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4464,63 +4464,63 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4894,63 +4894,63 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-12.42</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.25</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5324,63 +5324,63 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.86</v>
+        <v>18.74</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.04</v>
+        <v>19.01</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>-46.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.24</t>
+          <t>-104.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1737.831140350877</t>
+          <t>1735.478102189781</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>66.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>145.88</v>
+        <v>147.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11.15887376980629</t>
+          <t>-10.28890369105602</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-15.74382468564805</t>
+          <t>-5.504068257929575</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>248</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2.344673261373195</t>
+          <t>-2.733063144405144</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1.368909039925668</t>
+          <t>-4.869207501080865</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1539,29 +1539,29 @@
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2.522084938000019</t>
+          <t>-2.344673261373195</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1.537549798864816</t>
+          <t>-1.368909039925668</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3.260200344702716</t>
+          <t>-2.522084938000019</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>5.634721361463207</t>
+          <t>1.537549798864816</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3594,141 +3594,141 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>27.27</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>27.27</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-3.37</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-2.93</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>1733.088192419825</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>27.27</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>18.18</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-4.12</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-2.81</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>17.61</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>18.37</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>1735.478102189781</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG8" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.31</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.74</v>
+        <v>18.64</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.73</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.80</t>
+          <t>-105.43</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1735.478102189781</t>
+          <t>1733.088192419825</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>83.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>147.56</v>
+        <v>147.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-10.28890369105602</t>
+          <t>-9.85963190044408</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-5.504068257929575</t>
+          <t>-7.498637052078394</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,14 +1014,14 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF2" t="inlineStr">
         <is>
           <t>32.0</t>
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2.733063144405144</t>
+          <t>-3.950697466244736</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-4.869207501080865</t>
+          <t>-10.64768623636249</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,63 +1444,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2.344673261373195</t>
+          <t>-2.733063144405144</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1.368909039925668</t>
+          <t>-4.869207501080865</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1969,29 +1969,29 @@
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2.522084938000019</t>
+          <t>-2.344673261373195</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1.537549798864816</t>
+          <t>-1.368909039925668</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,14 +2304,14 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3.260200344702716</t>
+          <t>-2.522084938000019</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5.634721361463207</t>
+          <t>1.537549798864816</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200344702716</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.634721361463207</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458836732884</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559312019938</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622386680692</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701290561</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -4024,14 +4024,14 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF9" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -4039,126 +4039,126 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>1730.60480349345</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-6.917564584493647</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-9.995558126169087</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>1733.088192419825</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG9" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,14 +4454,14 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF10" t="inlineStr">
         <is>
           <t>27.27</t>
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929395098112</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599375176838</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-59.68</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.82908030781107</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577389639848</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.64</v>
+        <v>18.52</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.99</v>
+        <v>18.95</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-59.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.43</t>
+          <t>-106.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1733.088192419825</t>
+          <t>1730.60480349345</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>92.40000000000001</v>
+        <v>112.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>104.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>147.2</v>
+        <v>149.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-9.85963190044408</t>
+          <t>-9.047745343711238</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-7.498637052078394</t>
+          <t>-4.582369281680613</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,69 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>29.33</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-5.42</t>
-        </is>
+          <t>46.67</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-4.56</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-15.72</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.53</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
+          <t>-2.90</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.46</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3.950697466244736</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-10.64768623636249</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1263,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,7 +1441,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,59 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18.67</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-5.41</t>
-        </is>
+          <t>29.33</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-5.42</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-22.01</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
+          <t>-15.72</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.46</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2.733063144405144</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-4.869207501080865</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1706,7 +1690,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,69 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-5.58</t>
-        </is>
+          <t>18.67</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-5.41</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-29.34</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
+          <t>-22.01</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.44</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2.344673261373195</t>
+          <t>-2.733063143782822</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1.368909039925668</t>
+          <t>-4.869207500947056</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,7 +2149,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,7 +2259,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2293,7 +2269,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,69 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-4.83</t>
-        </is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-5.58</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-35.21</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
+          <t>-29.34</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.42</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,7 +2358,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2399,29 +2367,29 @@
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2.522084938000019</t>
+          <t>-2.344673260662052</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1.537549798864816</t>
+          <t>-1.368909039772745</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,7 +2707,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2752,56 +2720,48 @@
           <t>3.45</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-2.36</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-3.93</t>
-        </is>
+      <c r="AH6" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-4.83</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-31.29</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
+          <t>-35.21</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.39</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3.260200344702716</t>
+          <t>-2.52208493718738</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5.634721361463207</t>
+          <t>1.537549799039581</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,69 +3129,61 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.54</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-1.54</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-3.51</t>
-        </is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-3.93</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-31.02</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
+          <t>-31.29</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.35</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4.877458836732884</t>
+          <t>-3.260200343774101</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3.820559312019938</t>
+          <t>5.63472136166294</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3426,12 +3378,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,69 +3551,61 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>18.18</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-2.45</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-3.89</t>
-        </is>
+          <t>12.54</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-3.51</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-34.40</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
+          <t>-31.02</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.32</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5.069622386680692</t>
+          <t>-4.877458835671744</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.094059701290561</t>
+          <t>-3.820559311791669</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,69 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>27.27</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-3.37</t>
-        </is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-3.89</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-28.65</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
+          <t>-34.40</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6.917564584493647</t>
+          <t>-5.069622385468121</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-9.995558126169087</t>
+          <t>5.094059701551444</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4286,12 +4222,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4348,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4433,7 +4369,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4459,7 +4395,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,126 +4405,118 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>18.18</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-4.12</t>
-        </is>
+          <t>27.27</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-3.37</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-28.65</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-108.61</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>1728.353197674419</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-6.917564583108042</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-9.995558125870943</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-37.40</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-107.99</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>1730.60480349345</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>97.7</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-6.357929395098112</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-3.766599375176838</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
       <c r="BG10" t="inlineStr">
         <is>
           <t>2025/09/30</t>
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4817,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,59 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>22.22</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-3.58</t>
-        </is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-4.12</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-47.71</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
+          <t>-37.40</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.25</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6.82908030781107</t>
+          <t>-6.357929393514787</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5.373577389639848</t>
+          <t>-3.766599374836105</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,17 +5056,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,69 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13.13</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-3.78</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-2.90</t>
-        </is>
+          <t>22.22</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-3.58</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.52</v>
+        <v>18.43</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.95</v>
+        <v>18.93</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-59.68</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
+          <t>-47.71</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.23</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.38</t>
+          <t>-107.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1730.60480349345</t>
+          <t>1728.353197674419</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>112.6</v>
+        <v>129.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>109.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>149.36</v>
+        <v>153.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-9.047745343711238</t>
+          <t>-6.829080306001821</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-4.582369281680613</t>
+          <t>5.373577390029254</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>231.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>258</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5483,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,58 +1019,58 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>65.82</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4.56</v>
+        <v>-3.24</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.72</v>
+        <v>17.65</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.51</v>
+        <v>18.48</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="AR2" t="n">
         <v>-0.46</v>
@@ -1082,53 +1082,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.54</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>74.2</v>
+        <v>78.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.54</v>
+        <v>146.34</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.373886962522906</t>
+          <t>-4.47736797387843</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-6.701429195048107</t>
+          <t>-5.046513536333805</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,58 +1441,58 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.54</v>
+        <v>3.19</v>
       </c>
       <c r="AI3" t="n">
-        <v>-5.42</v>
+        <v>-4.56</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-15.72</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="AR3" t="n">
         <v>-0.46</v>
@@ -1504,53 +1504,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3.950697465700142</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-10.64768623624541</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="AI4" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,53 +1926,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2.733063143782822</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-4.869207500947056</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,61 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.71</v>
+        <v>0.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>-5.58</v>
+        <v>-5.41</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="AQ5" t="n">
         <v>-0.54</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,53 +2348,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2.344673260662052</t>
+          <t>-2.733063143782822</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1.368909039772745</t>
+          <t>-4.869207500947056</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,61 +2707,61 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-3.57</v>
+        <v>-0.71</v>
       </c>
       <c r="AI6" t="n">
-        <v>-4.83</v>
+        <v>-5.58</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,17 +2770,17 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2789,29 +2789,29 @@
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2.52208493718738</t>
+          <t>-2.344673260662052</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1.537549799039581</t>
+          <t>-1.368909039772745</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-2.36</v>
+        <v>-3.57</v>
       </c>
       <c r="AI7" t="n">
-        <v>-3.93</v>
+        <v>-4.83</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,53 +3192,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3.260200343774101</t>
+          <t>-2.52208493718738</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5.63472136166294</t>
+          <t>1.537549799039581</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,61 +3551,61 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-1.54</v>
+        <v>-2.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3.51</v>
+        <v>-3.93</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.42</v>
+        <v>-0.46</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4.877458835671744</t>
+          <t>-3.260200343774101</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3.820559311791669</t>
+          <t>5.63472136166294</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,61 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-2.45</v>
+        <v>-1.54</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.89</v>
+        <v>-3.51</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.4</v>
+        <v>-0.42</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,53 +4036,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-5.069622385468121</t>
+          <t>-4.877458835671744</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5.094059701551444</t>
+          <t>-3.820559311791669</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,61 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.28</v>
+        <v>-2.45</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.37</v>
+        <v>-3.89</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.35</v>
+        <v>-0.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,53 +4458,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6.917564583108042</t>
+          <t>-5.069622385468121</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-9.995558125870943</t>
+          <t>5.094059701551444</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4827,51 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.12</v>
+        <v>-3.37</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-37.40</t>
+          <t>-28.65</t>
         </is>
       </c>
       <c r="AQ11" t="n">
         <v>-0.35</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,53 +4880,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.99</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>128.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>152.7</v>
+        <v>152.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6.357929393514787</t>
+          <t>-6.917564583108042</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3.766599374836105</t>
+          <t>-9.995558125870943</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,51 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.11</v>
+        <v>0.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.58</v>
+        <v>-4.12</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.43</v>
+        <v>18.37</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.93</v>
+        <v>18.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-37.40</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,53 +5302,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.24</t>
+          <t>-107.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1728.353197674419</t>
+          <t>1726.071117561684</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>129.6</v>
+        <v>128.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>109.4</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>153.1</v>
+        <v>152.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6.829080306001821</t>
+          <t>-6.357929393514787</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.373577390029254</t>
+          <t>-3.766599374836105</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>231.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,17 +5478,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>77.96</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3.24</v>
+        <v>-2.39</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.65</v>
+        <v>17.57</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.10</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -1105,30 +1105,30 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>146.34</v>
+        <v>143.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.47736797387843</t>
+          <t>-4.598066706639509</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-5.046513536333805</t>
+          <t>-5.261909736825444</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,63 +1436,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>65.82</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="AI3" t="n">
-        <v>-4.56</v>
+        <v>-3.24</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.72</v>
+        <v>17.65</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.51</v>
+        <v>18.48</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="AR3" t="n">
         <v>-0.46</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.54</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>74.2</v>
+        <v>78.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.54</v>
+        <v>146.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.373886962522906</t>
+          <t>-4.47736797387843</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-6.701429195048107</t>
+          <t>-5.046513536333805</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,63 +1858,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.54</v>
+        <v>3.19</v>
       </c>
       <c r="AI4" t="n">
-        <v>-5.42</v>
+        <v>-4.56</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-15.72</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.46</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3.950697465700142</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10.64768623624541</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="AI5" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2.733063143782822</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-4.869207500947056</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.71</v>
+        <v>0.12</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5.58</v>
+        <v>-5.41</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="AQ6" t="n">
         <v>-0.54</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2.344673260662052</t>
+          <t>-2.733063143782822</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1.368909039772745</t>
+          <t>-4.869207500947056</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-3.57</v>
+        <v>-0.71</v>
       </c>
       <c r="AI7" t="n">
-        <v>-4.83</v>
+        <v>-5.58</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3211,29 +3211,29 @@
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2.52208493718738</t>
+          <t>-2.344673260662052</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1.537549799039581</t>
+          <t>-1.368909039772745</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3565,47 +3565,47 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-2.36</v>
+        <v>-3.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3.93</v>
+        <v>-4.83</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3.260200343774101</t>
+          <t>-2.52208493718738</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5.63472136166294</t>
+          <t>1.537549799039581</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-1.54</v>
+        <v>-2.36</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.51</v>
+        <v>-3.93</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.42</v>
+        <v>-0.46</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4.877458835671744</t>
+          <t>-3.260200343774101</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3.820559311791669</t>
+          <t>5.63472136166294</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-2.45</v>
+        <v>-1.54</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.89</v>
+        <v>-3.51</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.4</v>
+        <v>-0.42</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-5.069622385468121</t>
+          <t>-4.877458835671744</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.094059701551444</t>
+          <t>-3.820559311791669</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.28</v>
+        <v>-2.45</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.37</v>
+        <v>-3.89</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.35</v>
+        <v>-0.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6.917564583108042</t>
+          <t>-5.069622385468121</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-9.995558125870943</t>
+          <t>5.094059701551444</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -5234,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,51 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.12</v>
+        <v>-3.37</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.37</v>
+        <v>18.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.9</v>
+        <v>18.87</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-37.40</t>
+          <t>-28.65</t>
         </is>
       </c>
       <c r="AQ12" t="n">
         <v>-0.35</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.99</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1726.071117561684</t>
+          <t>1723.752173913044</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>128.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>152.7</v>
+        <v>152.68</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6.357929393514787</t>
+          <t>-6.917564583108042</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3.766599374836105</t>
+          <t>-9.995558125870943</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>253</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,38 +1014,38 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>77.96</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2.39</v>
+        <v>-1.82</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,26 +1054,26 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.57</v>
+        <v>17.47</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.43</v>
+        <v>18.39</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AQ2" t="n">
         <v>-0.41</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.10</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>78.2</v>
+        <v>75.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>143.02</v>
+        <v>137.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4.598066706639509</t>
+          <t>-5.072385572348653</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-5.261909736825444</t>
+          <t>-7.681139333748945</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>77.96</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-3.24</v>
+        <v>-2.39</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.65</v>
+        <v>17.57</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.10</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
@@ -1527,30 +1527,30 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>146.34</v>
+        <v>143.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.47736797387843</t>
+          <t>-4.598066706639509</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-5.046513536333805</t>
+          <t>-5.261909736825444</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,63 +1858,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>65.82</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4.56</v>
+        <v>-3.24</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.72</v>
+        <v>17.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.51</v>
+        <v>18.48</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="AR4" t="n">
         <v>-0.46</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.54</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>74.2</v>
+        <v>78.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.54</v>
+        <v>146.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.373886962522906</t>
+          <t>-4.47736797387843</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-6.701429195048107</t>
+          <t>-5.046513536333805</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,63 +2280,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.54</v>
+        <v>3.19</v>
       </c>
       <c r="AI5" t="n">
-        <v>-5.42</v>
+        <v>-4.56</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-15.72</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.46</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3.950697465700142</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10.64768623624541</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2.733063143782822</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-4.869207500947056</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.71</v>
+        <v>0.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>-5.58</v>
+        <v>-5.41</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="AQ7" t="n">
         <v>-0.54</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2.344673260662052</t>
+          <t>-2.733063143782822</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1.368909039772745</t>
+          <t>-4.869207500947056</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-3.57</v>
+        <v>-0.71</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.83</v>
+        <v>-5.58</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -3633,29 +3633,29 @@
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2.52208493718738</t>
+          <t>-2.344673260662052</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1.537549799039581</t>
+          <t>-1.368909039772745</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3987,47 +3987,47 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-2.36</v>
+        <v>-3.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.93</v>
+        <v>-4.83</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3.260200343774101</t>
+          <t>-2.52208493718738</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5.63472136166294</t>
+          <t>1.537549799039581</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,102 +4284,102 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-7.82</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-9.60</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-5.07</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>28.89</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>-0.58</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-8.00</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-1.54</v>
+        <v>-2.36</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.51</v>
+        <v>-3.93</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.42</v>
+        <v>-0.46</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4.877458835671744</t>
+          <t>-3.260200343774101</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3.820559311791669</t>
+          <t>5.63472136166294</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-2.45</v>
+        <v>-1.54</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.89</v>
+        <v>-3.51</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.4</v>
+        <v>-0.42</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5.069622385468121</t>
+          <t>-4.877458835671744</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5.094059701551444</t>
+          <t>-3.820559311791669</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-8.80</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.28</v>
+        <v>-2.45</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.37</v>
+        <v>-3.89</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.32</v>
+        <v>18.24</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.87</v>
+        <v>18.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.35</v>
+        <v>-0.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-109.42</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1723.752173913044</t>
+          <t>1721.370477568741</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>93.40000000000001</v>
+        <v>134</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>152.68</v>
+        <v>150.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6.917564583108042</t>
+          <t>-5.069622385468121</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-9.995558125870943</t>
+          <t>5.094059701551444</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.21</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1024,56 +1024,56 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.46</v>
+        <v>-1.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.82</v>
+        <v>-1.19</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.47</v>
+        <v>17.37</v>
       </c>
       <c r="AN2" t="n">
-        <v>18.39</v>
+        <v>18.35</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-113.64</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1101,29 +1101,29 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>75.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>137.92</v>
+        <v>135.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5.072385572348653</t>
+          <t>-5.704721879410656</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-7.681139333748945</t>
+          <t>-9.182571568251674</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1446,28 +1446,28 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>77.96</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2.39</v>
+        <v>-1.82</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1476,26 +1476,26 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.57</v>
+        <v>17.47</v>
       </c>
       <c r="AN3" t="n">
-        <v>18.43</v>
+        <v>18.39</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AQ3" t="n">
         <v>-0.41</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.10</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>78.2</v>
+        <v>75.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>143.02</v>
+        <v>137.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4.598066706639509</t>
+          <t>-5.072385572348653</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-5.261909736825444</t>
+          <t>-7.681139333748945</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1868,56 +1868,56 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>77.96</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3.24</v>
+        <v>-2.39</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.65</v>
+        <v>17.57</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.10</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
@@ -1949,30 +1949,30 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>146.34</v>
+        <v>143.02</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4.47736797387843</t>
+          <t>-4.598066706639509</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5.046513536333805</t>
+          <t>-5.261909736825444</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2290,53 +2290,53 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>65.82</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4.56</v>
+        <v>-3.24</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.72</v>
+        <v>17.65</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.51</v>
+        <v>18.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.46</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-114.54</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>74.2</v>
+        <v>78.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>146.54</v>
+        <v>146.34</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4.373886962522906</t>
+          <t>-4.47736797387843</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-6.701429195048107</t>
+          <t>-5.046513536333805</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2712,53 +2712,53 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.54</v>
+        <v>3.19</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5.42</v>
+        <v>-4.56</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-15.72</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="AR6" t="n">
         <v>-0.46</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3.950697465700142</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-10.64768623624541</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="AI7" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2.733063143782822</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-4.869207500947056</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3556,56 +3556,56 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.71</v>
+        <v>0.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5.58</v>
+        <v>-5.41</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AN8" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="AQ8" t="n">
         <v>-0.54</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2.344673260662052</t>
+          <t>-2.733063143782822</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1.368909039772745</t>
+          <t>-4.869207500947056</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3978,56 +3978,56 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-3.57</v>
+        <v>-0.71</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.83</v>
+        <v>-5.58</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AN9" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -4055,29 +4055,29 @@
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2.52208493718738</t>
+          <t>-2.344673260662052</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1.537549799039581</t>
+          <t>-1.368909039772745</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4409,47 +4409,47 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-2.36</v>
+        <v>-3.57</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.93</v>
+        <v>-4.83</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3.260200343774101</t>
+          <t>-2.52208493718738</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5.63472136166294</t>
+          <t>1.537549799039581</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-7.82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4822,56 +4822,56 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.54</v>
+        <v>-2.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.51</v>
+        <v>-3.93</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.29</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.42</v>
+        <v>-0.46</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.21</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>112</v>
+        <v>110.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>145.48</v>
+        <v>146.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4.877458835671744</t>
+          <t>-3.260200343774101</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3.820559311791669</t>
+          <t>5.63472136166294</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>225.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>-8.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5244,56 +5244,56 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.45</v>
+        <v>-1.54</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.89</v>
+        <v>-3.51</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.24</v>
+        <v>18.16</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.83</v>
+        <v>18.79</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.4</v>
+        <v>-0.42</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.42</t>
+          <t>-110.21</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1721.370477568741</t>
+          <t>1718.995664739884</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>150.4</v>
+        <v>145.48</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5.069622385468121</t>
+          <t>-4.877458835671744</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5.094059701551444</t>
+          <t>-3.820559311791669</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>15.21</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1099,61 +1099,61 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-2.77</v>
+        <v>2.47</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.64</v>
+        <v>-1.25</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>17.25</v>
+        <v>17.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>18.3</v>
+        <v>18.27</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-0.43</v>
+        <v>-0.37</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-113.60</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>82.2</v>
+        <v>101.6</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>134.94</v>
+        <v>134.86</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-5.593073873839368</t>
+          <t>-4.080607337799354</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-4.979009843197289</t>
+          <t>4.237958610420719</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1561,58 +1561,58 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-1.22</v>
+        <v>-2.77</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.19</v>
+        <v>-1.64</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>17.37</v>
+        <v>17.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>18.35</v>
+        <v>18.3</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-0.4</v>
+        <v>-0.43</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0.43</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-113.64</t>
+          <t>-113.60</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>82.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>135.22</v>
+        <v>134.94</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-5.704721879410656</t>
+          <t>-5.593073873839368</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-9.182571568251674</t>
+          <t>-4.979009843197289</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,17 +1735,17 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2023,61 +2023,61 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-1.46</v>
+        <v>-1.22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.82</v>
+        <v>-1.19</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>17.47</v>
+        <v>17.37</v>
       </c>
       <c r="AV4" t="n">
-        <v>18.39</v>
+        <v>18.35</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-113.64</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2105,29 +2105,29 @@
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>75.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>137.92</v>
+        <v>135.22</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-5.072385572348653</t>
+          <t>-5.704721879410656</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-7.681139333748945</t>
+          <t>-9.182571568251674</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,17 +2197,17 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2485,33 +2485,33 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>77.96</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2.39</v>
+        <v>-1.82</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -2520,26 +2520,26 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>17.57</v>
+        <v>17.47</v>
       </c>
       <c r="AV5" t="n">
-        <v>18.43</v>
+        <v>18.39</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AY5" t="n">
         <v>-0.41</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-114.10</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>78.2</v>
+        <v>75.8</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>143.02</v>
+        <v>137.92</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-4.598066706639509</t>
+          <t>-5.072385572348653</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-5.261909736825444</t>
+          <t>-7.681139333748945</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2947,61 +2947,61 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>77.96</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-3.24</v>
+        <v>-2.39</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>17.65</v>
+        <v>17.57</v>
       </c>
       <c r="AV6" t="n">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.10</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
@@ -3033,30 +3033,30 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>146.34</v>
+        <v>143.02</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-4.47736797387843</t>
+          <t>-4.598066706639509</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-5.046513536333805</t>
+          <t>-5.261909736825444</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3409,58 +3409,58 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>65.82</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-4.56</v>
+        <v>-3.24</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>17.72</v>
+        <v>17.65</v>
       </c>
       <c r="AV7" t="n">
-        <v>18.51</v>
+        <v>18.48</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0.46</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-114.54</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>74.2</v>
+        <v>78.2</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>146.54</v>
+        <v>146.34</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-4.373886962522906</t>
+          <t>-4.47736797387843</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-6.701429195048107</t>
+          <t>-5.046513536333805</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3871,58 +3871,58 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.54</v>
+        <v>3.19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-5.42</v>
+        <v>-4.56</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-15.72</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="AZ8" t="n">
         <v>-0.46</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-3.950697465700142</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-10.64768623624541</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4115,17 +4115,17 @@
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4343,51 +4343,51 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AV9" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-2.733063143782822</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-4.869207500947056</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4795,61 +4795,61 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-0.71</v>
+        <v>0.12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-5.58</v>
+        <v>-5.41</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AV10" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="AY10" t="n">
         <v>-0.54</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-2.344673260662052</t>
+          <t>-2.733063143782822</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-1.368909039772745</t>
+          <t>-4.869207500947056</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5257,61 +5257,61 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-3.57</v>
+        <v>-0.71</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-4.83</v>
+        <v>-5.58</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AV11" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5339,29 +5339,29 @@
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-2.52208493718738</t>
+          <t>-2.344673260662052</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>1.537549799039581</t>
+          <t>-1.368909039772745</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5733,47 +5733,47 @@
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>-2.36</v>
+        <v>-3.57</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-3.93</v>
+        <v>-4.83</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>18.07</v>
+        <v>17.98</v>
       </c>
       <c r="AV12" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-31.29</t>
+          <t>-35.21</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-0.46</v>
+        <v>-0.52</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-112.15</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1716.772727272727</t>
+          <t>1714.733429394813</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>110.8</v>
+        <v>124</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>126.4</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>146.4</v>
+        <v>146.22</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-3.260200343774101</t>
+          <t>-2.52208493718738</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>5.63472136166294</t>
+          <t>1.537549799039581</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>257</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>26.67</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>5.45</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>94.74</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>47.37</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>2.47</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>-1.25</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-5.89</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-1.54</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>16.98</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>17.2</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>18.27</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>18.56</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>12.08</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.37</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.42</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-113.20</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>101.6</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>89.9</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>134.86</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-4.080607337799354</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>4.237958610420719</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>201.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-8.18</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>16.85</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>17.4</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>16.5</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>17.4</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>15.56</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-1.82</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>29.82</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-2.77</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>-1.64</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-5.72</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-1.47</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>16.97</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>17.25</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>18.3</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>18.57</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.43</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-0.43</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-113.60</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>119.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>82.2</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>78.2</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>134.94</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-5.593073873839368</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-4.979009843197289</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>119.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-12.93</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>16.55</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>16.5</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>16.5</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>6.67</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>47.37</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>52.63</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-1.22</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-1.19</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-5.35</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-1.38</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>17.16</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>17.37</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>18.35</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>18.6</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>7.01</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.43</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-113.64</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>88.8</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>135.22</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-5.704721879410656</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-9.182571568251674</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-10.55</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>17.2</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>17.2</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>16.7</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>16.95</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>6.67</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>42.11</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-1.46</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>-1.82</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-5.02</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-1.31</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>17.47</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>18.39</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>18.64</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>6.43</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.41</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.44</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-113.88</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>75.8</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>85.3</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>137.92</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-5.072385572348653</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-7.681139333748945</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-10.82</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價跌量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>2.03</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>16.85</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>16.85</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>11.11</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>2.71</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>68.42</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>77.96</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-2.39</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-4.69</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>17.57</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>18.43</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>18.67</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>7.66</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.41</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-0.45</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-114.10</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>78.2</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>107.6</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>143.02</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-29</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-4.598066706639509</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-5.261909736825444</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-9.50</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>2.06</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>16.65</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>17.2</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>16.65</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>2.70</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>89.47</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>65.82</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>1.58</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-3.24</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-4.46</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-1.14</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>17.08</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>17.65</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>18.48</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>18.69</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>4.81</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.43</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-0.46</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-114.37</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>78.2</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>101.1</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>146.34</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-22</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-4.47736797387843</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-5.046513536333805</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-8.44</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>17.35</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>15.56</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>5.12</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>76.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>46.67</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>3.19</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-4.56</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-4.28</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-1.08</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>16.91</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>17.72</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>18.51</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>18.71</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>-2.90</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-0.46</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-114.54</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>74.2</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>92.5</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>146.54</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-4.373886962522906</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-6.701429195048107</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-7.92</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>16.6</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>2.22</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>29.33</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.54</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-5.42</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-4.16</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-1.02</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>16.81</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>17.77</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>18.54</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>18.73</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>-15.72</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.53</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-0.46</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-114.44</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>95</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>146.98</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-3.950697465700142</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-10.64768623624541</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-10.82</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>2.03</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>8.89</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>3.36</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>18.67</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>0.12</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-5.41</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-4.01</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-0.91</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>16.88</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>17.84</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>18.59</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>18.76</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>-22.01</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-0.54</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-0.44</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-113.87</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>94.8</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>114.4</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>147.02</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-2.733063143782822</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-4.869207500947056</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-10.82</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>2.03</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>16.35</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>11.11</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-0.71</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-5.58</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-3.86</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-0.82</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>16.92</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>17.92</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>18.64</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>18.79</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>-29.34</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-0.54</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-0.42</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-113.11</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>137</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>115.2</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>146.36</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-2.344673260662052</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-1.368909039772745</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-11.35</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>16.85</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>16.85</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>16.6</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/11/06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/04/18</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>22.0</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>11.11</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-0.30</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>3.45</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-3.57</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-4.83</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-3.8</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-0.70</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>17.11</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>17.98</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>18.69</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>18.82</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>-35.21</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-0.52</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-0.39</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-112.15</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>1714.733429394813</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>124</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>126.4</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>146.22</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-2.52208493718738</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>1.537549799039581</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>84.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-12.93</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.43</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
         <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
         <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>15.17</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>16.55</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>16.55</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>16.5</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>16.5</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,51 +1149,51 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1.25</v>
+        <v>-0.99</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.7</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="AY2" t="n">
         <v>17.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.27</v>
+        <v>18.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.37</v>
+        <v>-0.32</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-113.20</t>
+          <t>-112.57</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>101.6</v>
+        <v>88.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>134.86</v>
+        <v>131</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-4.080607337799354</t>
+          <t>-3.947608122339021</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>4.237958610420719</t>
+          <t>-3.216112437307189</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,61 +1621,61 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-2.77</v>
+        <v>2.47</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.64</v>
+        <v>-1.25</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>17.25</v>
+        <v>17.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.3</v>
+        <v>18.27</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.43</v>
+        <v>-0.37</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-113.60</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>82.2</v>
+        <v>101.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>134.94</v>
+        <v>134.86</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-5.593073873839368</t>
+          <t>-4.080607337799354</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-4.979009843197289</t>
+          <t>4.237958610420719</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,58 +2103,58 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1.22</v>
+        <v>-2.77</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.19</v>
+        <v>-1.64</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>17.37</v>
+        <v>17.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18.35</v>
+        <v>18.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.4</v>
+        <v>-0.43</v>
       </c>
       <c r="BD4" t="n">
         <v>-0.43</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-113.64</t>
+          <t>-113.60</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>82.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>135.22</v>
+        <v>134.94</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-5.704721879410656</t>
+          <t>-5.593073873839368</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-9.182571568251674</t>
+          <t>-4.979009843197289</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,61 +2585,61 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1.46</v>
+        <v>-1.22</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.82</v>
+        <v>-1.19</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>17.47</v>
+        <v>17.37</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18.39</v>
+        <v>18.35</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-113.64</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2667,29 +2667,29 @@
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>75.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>137.92</v>
+        <v>135.22</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-5.072385572348653</t>
+          <t>-5.704721879410656</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-7.681139333748945</t>
+          <t>-9.182571568251674</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,33 +3067,33 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>77.96</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="AU6" t="n">
-        <v>-2.39</v>
+        <v>-1.82</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -3102,26 +3102,26 @@
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>17.57</v>
+        <v>17.47</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.43</v>
+        <v>18.39</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BC6" t="n">
         <v>-0.41</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-114.10</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>78.2</v>
+        <v>75.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>143.02</v>
+        <v>137.92</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-4.598066706639509</t>
+          <t>-5.072385572348653</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-5.261909736825444</t>
+          <t>-7.681139333748945</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,61 +3549,61 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>77.96</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>-3.24</v>
+        <v>-2.39</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>17.65</v>
+        <v>17.57</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.10</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
@@ -3635,30 +3635,30 @@
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>146.34</v>
+        <v>143.02</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-4.47736797387843</t>
+          <t>-4.598066706639509</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-5.046513536333805</t>
+          <t>-5.261909736825444</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,58 +4031,58 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>65.82</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="AU8" t="n">
-        <v>-4.56</v>
+        <v>-3.24</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>17.72</v>
+        <v>17.65</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.51</v>
+        <v>18.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="BD8" t="n">
         <v>-0.46</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-114.54</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>74.2</v>
+        <v>78.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>146.54</v>
+        <v>146.34</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-4.373886962522906</t>
+          <t>-4.47736797387843</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-6.701429195048107</t>
+          <t>-5.046513536333805</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,58 +4513,58 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.54</v>
+        <v>3.19</v>
       </c>
       <c r="AU9" t="n">
-        <v>-5.42</v>
+        <v>-4.56</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-15.72</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="BD9" t="n">
         <v>-0.46</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3.950697465700142</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-10.64768623624541</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
@@ -4757,17 +4757,17 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5005,51 +5005,51 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="AU10" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2.733063143782822</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-4.869207500947056</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,61 +5477,61 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.71</v>
+        <v>0.12</v>
       </c>
       <c r="AU11" t="n">
-        <v>-5.58</v>
+        <v>-5.41</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="BC11" t="n">
         <v>-0.54</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-2.344673260662052</t>
+          <t>-2.733063143782822</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1.368909039772745</t>
+          <t>-4.869207500947056</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,61 +5959,61 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-3.57</v>
+        <v>-0.71</v>
       </c>
       <c r="AU12" t="n">
-        <v>-4.83</v>
+        <v>-5.58</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>17.98</v>
+        <v>17.92</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18.69</v>
+        <v>18.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>18.79</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-35.21</t>
+          <t>-29.34</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-112.15</t>
+          <t>-113.11</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1714.733429394813</t>
+          <t>1712.302877697842</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -6041,29 +6041,29 @@
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>126.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>146.22</v>
+        <v>146.36</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2.52208493718738</t>
+          <t>-2.344673260662052</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>1.537549799039581</t>
+          <t>-1.368909039772745</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -943,42 +943,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-3.05</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,33 +1139,33 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>77.19</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2.17</v>
+        <v>-0.76</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.99</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1174,26 +1174,26 @@
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>17.2</v>
+        <v>17.15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.24</v>
+        <v>18.19</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BC2" t="n">
         <v>-0.32</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-112.57</t>
+          <t>-112.05</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>88.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>131</v>
+        <v>125.56</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-3.947608122339021</t>
+          <t>-3.679292928099795</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-3.216112437307189</t>
+          <t>-2.203559359784052</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1631,51 +1631,51 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.25</v>
+        <v>-0.99</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.7</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="AY3" t="n">
         <v>17.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.27</v>
+        <v>18.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.37</v>
+        <v>-0.32</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-113.20</t>
+          <t>-112.57</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>101.6</v>
+        <v>88.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>134.86</v>
+        <v>131</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-4.080607337799354</t>
+          <t>-3.947608122339021</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>4.237958610420719</t>
+          <t>-3.216112437307189</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,61 +2103,61 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-2.77</v>
+        <v>2.47</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.64</v>
+        <v>-1.25</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>17.25</v>
+        <v>17.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18.3</v>
+        <v>18.27</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.43</v>
+        <v>-0.37</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-113.60</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>82.2</v>
+        <v>101.6</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>134.94</v>
+        <v>134.86</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-5.593073873839368</t>
+          <t>-4.080607337799354</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-4.979009843197289</t>
+          <t>4.237958610420719</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,58 +2585,58 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1.22</v>
+        <v>-2.77</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.19</v>
+        <v>-1.64</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>17.37</v>
+        <v>17.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18.35</v>
+        <v>18.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.4</v>
+        <v>-0.43</v>
       </c>
       <c r="BD5" t="n">
         <v>-0.43</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-113.64</t>
+          <t>-113.60</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>82.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>135.22</v>
+        <v>134.94</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-5.704721879410656</t>
+          <t>-5.593073873839368</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-9.182571568251674</t>
+          <t>-4.979009843197289</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,61 +3067,61 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.46</v>
+        <v>-1.22</v>
       </c>
       <c r="AU6" t="n">
-        <v>-1.82</v>
+        <v>-1.19</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>17.47</v>
+        <v>17.37</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.39</v>
+        <v>18.35</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-113.64</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -3149,29 +3149,29 @@
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>75.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>137.92</v>
+        <v>135.22</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-5.072385572348653</t>
+          <t>-5.704721879410656</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-7.681139333748945</t>
+          <t>-9.182571568251674</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,33 +3549,33 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>77.96</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="AU7" t="n">
-        <v>-2.39</v>
+        <v>-1.82</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3584,26 +3584,26 @@
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>17.57</v>
+        <v>17.47</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18.43</v>
+        <v>18.39</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BC7" t="n">
         <v>-0.41</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-114.10</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>78.2</v>
+        <v>75.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>143.02</v>
+        <v>137.92</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-4.598066706639509</t>
+          <t>-5.072385572348653</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-5.261909736825444</t>
+          <t>-7.681139333748945</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,61 +4031,61 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>77.96</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>-3.24</v>
+        <v>-2.39</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>17.65</v>
+        <v>17.57</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.10</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
@@ -4117,30 +4117,30 @@
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>146.34</v>
+        <v>143.02</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-4.47736797387843</t>
+          <t>-4.598066706639509</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-5.046513536333805</t>
+          <t>-5.261909736825444</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,58 +4513,58 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>65.82</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="AU9" t="n">
-        <v>-4.56</v>
+        <v>-3.24</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>17.72</v>
+        <v>17.65</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.51</v>
+        <v>18.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="BD9" t="n">
         <v>-0.46</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-114.54</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>74.2</v>
+        <v>78.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>146.54</v>
+        <v>146.34</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-4.373886962522906</t>
+          <t>-4.47736797387843</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-6.701429195048107</t>
+          <t>-5.046513536333805</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,58 +4995,58 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.54</v>
+        <v>3.19</v>
       </c>
       <c r="AU10" t="n">
-        <v>-5.42</v>
+        <v>-4.56</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-15.72</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="BD10" t="n">
         <v>-0.46</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-3.950697465700142</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-10.64768623624541</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5487,51 +5487,51 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="AU11" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-2.733063143782822</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-4.869207500947056</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>-17.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,61 +5959,61 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.71</v>
+        <v>0.12</v>
       </c>
       <c r="AU12" t="n">
-        <v>-5.58</v>
+        <v>-5.41</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>17.92</v>
+        <v>17.84</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>-22.01</t>
         </is>
       </c>
       <c r="BC12" t="n">
         <v>-0.54</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-113.11</t>
+          <t>-113.87</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1712.302877697842</t>
+          <t>1710.056034482759</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>137</v>
+        <v>94.8</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>114.4</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>146.36</v>
+        <v>147.02</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2.344673260662052</t>
+          <t>-2.733063143782822</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-1.368909039772745</t>
+          <t>-4.869207500947056</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>250</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.35</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,61 +1139,61 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>77.19</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.76</v>
+        <v>1.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.23</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AY2" t="n">
         <v>17.15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.19</v>
+        <v>18.15</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>18.49</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>23.92</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-112.05</t>
+          <t>-111.37</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>97.59999999999999</v>
+        <v>131.4</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>125.56</v>
+        <v>121.78</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-3.679292928099795</t>
+          <t>-1.927045280934172</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-2.203559359784052</t>
+          <t>7.710316778476752</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,33 +1621,33 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>77.19</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2.17</v>
+        <v>-0.76</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.99</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1656,26 +1656,26 @@
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>17.2</v>
+        <v>17.15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.24</v>
+        <v>18.19</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>-0.32</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-112.57</t>
+          <t>-112.05</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>88.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>131</v>
+        <v>125.56</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-3.947608122339021</t>
+          <t>-3.679292928099795</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-3.216112437307189</t>
+          <t>-2.203559359784052</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.25</v>
+        <v>-0.99</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.7</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="AY4" t="n">
         <v>17.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18.27</v>
+        <v>18.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.37</v>
+        <v>-0.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-113.20</t>
+          <t>-112.57</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>101.6</v>
+        <v>88.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>134.86</v>
+        <v>131</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-4.080607337799354</t>
+          <t>-3.947608122339021</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>4.237958610420719</t>
+          <t>-3.216112437307189</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.00</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,61 +2585,61 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-2.77</v>
+        <v>2.47</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.64</v>
+        <v>-1.25</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>17.25</v>
+        <v>17.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18.3</v>
+        <v>18.27</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.43</v>
+        <v>-0.37</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-113.60</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>82.2</v>
+        <v>101.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>134.94</v>
+        <v>134.86</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-5.593073873839368</t>
+          <t>-4.080607337799354</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-4.979009843197289</t>
+          <t>4.237958610420719</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-12.93</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,58 +3067,58 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.22</v>
+        <v>-2.77</v>
       </c>
       <c r="AU6" t="n">
-        <v>-1.19</v>
+        <v>-1.64</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>17.37</v>
+        <v>17.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.35</v>
+        <v>18.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.4</v>
+        <v>-0.43</v>
       </c>
       <c r="BD6" t="n">
         <v>-0.43</v>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-113.64</t>
+          <t>-113.60</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>82.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>135.22</v>
+        <v>134.94</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-5.704721879410656</t>
+          <t>-5.593073873839368</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-9.182571568251674</t>
+          <t>-4.979009843197289</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-12.93</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,152 +3378,152 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-6.98</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-9.60</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-5.07</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-11.14</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/04/18</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>18.75</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-9.87</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/04/18</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,61 +3549,61 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.46</v>
+        <v>-1.22</v>
       </c>
       <c r="AU7" t="n">
-        <v>-1.82</v>
+        <v>-1.19</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>17.47</v>
+        <v>17.37</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18.39</v>
+        <v>18.35</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-113.88</t>
+          <t>-113.64</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3631,29 +3631,29 @@
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>75.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>137.92</v>
+        <v>135.22</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-5.072385572348653</t>
+          <t>-5.704721879410656</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-7.681139333748945</t>
+          <t>-9.182571568251674</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-11.14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,33 +4031,33 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>68.42</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>77.96</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="AU8" t="n">
-        <v>-2.39</v>
+        <v>-1.82</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -4066,26 +4066,26 @@
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>17.57</v>
+        <v>17.47</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.43</v>
+        <v>18.39</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BC8" t="n">
         <v>-0.41</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.45</v>
+        <v>-0.44</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-114.10</t>
+          <t>-113.88</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>78.2</v>
+        <v>75.8</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>143.02</v>
+        <v>137.92</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-4.598066706639509</t>
+          <t>-5.072385572348653</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-5.261909736825444</t>
+          <t>-7.681139333748945</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,61 +4513,61 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>68.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>77.96</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>-3.24</v>
+        <v>-2.39</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>17.65</v>
+        <v>17.57</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.48</v>
+        <v>18.43</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.10</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
@@ -4599,30 +4599,30 @@
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>146.34</v>
+        <v>143.02</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-4.47736797387843</t>
+          <t>-4.598066706639509</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-5.046513536333805</t>
+          <t>-5.261909736825444</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4782,14 +4782,14 @@
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-22.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,58 +4995,58 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>65.82</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="AU10" t="n">
-        <v>-4.56</v>
+        <v>-3.24</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>17.72</v>
+        <v>17.65</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.51</v>
+        <v>18.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="BD10" t="n">
         <v>-0.46</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-114.54</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>74.2</v>
+        <v>78.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>146.54</v>
+        <v>146.34</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-4.373886962522906</t>
+          <t>-4.47736797387843</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-6.701429195048107</t>
+          <t>-5.046513536333805</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,58 +5477,58 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.54</v>
+        <v>3.19</v>
       </c>
       <c r="AU11" t="n">
-        <v>-5.42</v>
+        <v>-4.56</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-4.16</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>17.77</v>
+        <v>17.72</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-15.72</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="BD11" t="n">
         <v>-0.46</v>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-114.44</t>
+          <t>-114.54</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>95</v>
+        <v>74.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>146.98</v>
+        <v>146.54</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-3.950697465700142</t>
+          <t>-4.373886962522906</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-10.64768623624541</t>
+          <t>-6.701429195048107</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5721,17 +5721,17 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="CV11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-17.13</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,51 +5969,51 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="AU12" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>17.84</v>
+        <v>17.77</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-15.72</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-113.87</t>
+          <t>-114.44</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1710.056034482759</t>
+          <t>1708.078192252511</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>147.02</v>
+        <v>146.98</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2.733063143782822</t>
+          <t>-3.950697465700142</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-4.869207500947056</t>
+          <t>-10.64768623624541</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>256</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>16.35</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV12"/>
+  <dimension ref="A1:CW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,320 +611,325 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross_d</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -933,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1113,300 +1118,305 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2024-05-17 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>-5.43</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>77.1</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.4</v>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>78.85</t>
+        </is>
       </c>
       <c r="AU2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>-5.42</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>17.31</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>18.47</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>32.10</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
         <v>-0.23</v>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>17.15</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>18.49</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BE2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-111.37</t>
-        </is>
-      </c>
       <c r="BG2" t="inlineStr">
         <is>
+          <t>-110.52</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>221.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>131.4</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>121.78</v>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>102.2</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>121.68</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1.927045280934172</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>7.710316778476752</t>
+          <t>-1.114073367590853</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>3.357272155797403</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>-8.44</t>
-        </is>
-      </c>
       <c r="BU2" t="inlineStr">
         <is>
+          <t>-7.65</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>17.35</t>
-        </is>
-      </c>
       <c r="CT2" t="inlineStr">
         <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1425,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,300 +1605,305 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2024-05-17 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>77.19</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>-0.76</v>
+          <t>94.44</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>-5.72</t>
-        </is>
+        <v>1.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-0.23</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>17.03</t>
-        </is>
-      </c>
-      <c r="AY3" t="n">
+          <t>-1.83</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>17.11</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
         <v>17.15</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>18.51</t>
-        </is>
+      <c r="BA3" t="n">
+        <v>18.15</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>17.33</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-0.32</v>
+          <t>18.49</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>23.92</t>
+        </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="BE3" t="inlineStr">
+        <v>-0.27</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-112.05</t>
-        </is>
-      </c>
       <c r="BG3" t="inlineStr">
         <is>
+          <t>-111.37</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="BL3" t="n">
-        <v>125.56</v>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>221.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
+        <v>121.78</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-3.679292928099795</t>
+          <t>24</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2.203559359784052</t>
+          <t>-1.927045280934172</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>7.710316778476752</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>-10.82</t>
-        </is>
-      </c>
       <c r="BU3" t="inlineStr">
         <is>
+          <t>-8.44</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
+          <t>17.35</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1907,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,300 +2092,305 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2024-05-17 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>63.16</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.17</v>
+          <t>42.11</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>77.19</t>
+        </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>-5.7</t>
-        </is>
+        <v>-0.76</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
           <t>17.03</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>17.2</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>18.24</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>18.54</t>
-        </is>
+        <v>17.15</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>18.19</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20.11</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
+          <t>18.51</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>17.33</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
         <v>-0.32</v>
       </c>
-      <c r="BD4" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BE4" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="BF4" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-112.57</t>
-        </is>
-      </c>
       <c r="BG4" t="inlineStr">
         <is>
+          <t>-112.05</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
-      </c>
-      <c r="BL4" t="n">
-        <v>131</v>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="BM4" t="n">
+        <v>125.56</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-3.947608122339021</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3.216112437307189</t>
+          <t>-3.679292928099795</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>-2.203559359784052</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>-8.18</t>
-        </is>
-      </c>
       <c r="BU4" t="inlineStr">
         <is>
+          <t>-10.82</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2389,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2414,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2514,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,274 +2579,274 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2024-05-17 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
           <t>94.74</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>47.37</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.47</v>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>63.16</t>
+        </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>-5.89</t>
-        </is>
+        <v>2.17</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.99</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-5.7</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="AY5" t="n">
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>17.03</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
         <v>17.2</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>18.27</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>18.56</t>
-        </is>
+      <c r="BA5" t="n">
+        <v>18.24</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>12.08</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-0.37</v>
+          <t>18.54</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>20.11</t>
+        </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="BE5" t="inlineStr">
+        <v>-0.32</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="BF5" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>-113.20</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
+          <t>-112.57</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>201.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>89.9</t>
-        </is>
-      </c>
-      <c r="BL5" t="n">
-        <v>134.86</v>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
+        <v>131</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-4.080607337799354</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>4.237958610420719</t>
+          <t>-3.947608122339021</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>-3.216112437307189</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>-8.18</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>2.09</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
       <c r="CQ5" t="inlineStr">
         <is>
           <t>17.4</t>
@@ -2834,7 +2854,7 @@
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -2844,15 +2864,20 @@
       </c>
       <c r="CT5" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2871,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,455 +2911,460 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>13.01</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-7.20</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-5.07</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/04/18</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2024-05-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>26.67</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>5.45</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>94.74</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>-5.89</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>16.98</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>18.56</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>12.08</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-113.20</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>201.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>89.9</t>
+        </is>
+      </c>
+      <c r="BM6" t="n">
+        <v>134.86</v>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-4.080607337799354</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>4.237958610420719</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>201.0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>-8.18</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>-4.914704939634603</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>3.89524476612966</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>0.4035023817520423</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>30.08%</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>-1.36%</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>14.99</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>正能量智能-運動休閒-上櫃</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>運動休閒平上櫃</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>16.85</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
           <t>16.5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>5.12</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-12.00</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/04/18</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>29.82</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>-2.77</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>-5.72</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
-      </c>
-      <c r="AY6" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>18.57</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-113.60</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="BL6" t="n">
-        <v>134.94</v>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-5.593073873839368</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-4.979009843197289</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-12.93</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>-4.914704939634603</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>3.89524476612966</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>0.4035023817520423</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>30.08%</t>
-        </is>
-      </c>
-      <c r="CJ6" t="inlineStr">
-        <is>
-          <t>-1.36%</t>
-        </is>
-      </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN6" t="inlineStr">
-        <is>
-          <t>正能量智能-運動休閒-上櫃</t>
-        </is>
-      </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>運動休閒平上櫃</t>
-        </is>
-      </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
-      </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
       <c r="CT6" t="inlineStr">
         <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3353,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.60</t>
+          <t>-12.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,345 +3508,350 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/04/18</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2024-05-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>15.56</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/04/18</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>47.37</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>52.63</t>
-        </is>
-      </c>
-      <c r="AT7" t="n">
-        <v>-1.22</v>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>29.82</t>
+        </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>-5.35</t>
-        </is>
+        <v>-2.77</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-1.64</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>17.16</t>
-        </is>
-      </c>
-      <c r="AY7" t="n">
-        <v>17.37</v>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>16.97</t>
+        </is>
       </c>
       <c r="AZ7" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
+        <v>17.25</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>18.3</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-0.4</v>
+          <t>18.57</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
       </c>
       <c r="BD7" t="n">
         <v>-0.43</v>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BE7" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="BF7" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-113.64</t>
-        </is>
-      </c>
       <c r="BG7" t="inlineStr">
         <is>
+          <t>-113.60</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>88.8</t>
-        </is>
-      </c>
-      <c r="BL7" t="n">
-        <v>135.22</v>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="BM7" t="n">
+        <v>134.94</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-5.704721879410656</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-9.182571568251674</t>
+          <t>-5.593073873839368</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>-4.979009843197289</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>-10.55</t>
-        </is>
-      </c>
       <c r="BU7" t="inlineStr">
         <is>
+          <t>-12.93</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3835,7 +3870,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3850,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-9.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,300 +4040,305 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2024-05-17 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
           <t>6.67</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>66.67</t>
-        </is>
-      </c>
-      <c r="AT8" t="n">
-        <v>-1.46</v>
+          <t>47.37</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>52.63</t>
+        </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.82</v>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>-5.02</t>
-        </is>
+        <v>-1.22</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-1.19</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17.15</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>17.47</v>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>17.16</t>
+        </is>
       </c>
       <c r="AZ8" t="n">
-        <v>18.39</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
+        <v>17.37</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>18.35</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-0.41</v>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="BE8" t="inlineStr">
+        <v>-0.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="BF8" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-113.88</t>
-        </is>
-      </c>
       <c r="BG8" t="inlineStr">
         <is>
+          <t>-113.64</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
       <c r="BI8" t="inlineStr">
         <is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="BJ8" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>85.3</t>
-        </is>
-      </c>
-      <c r="BL8" t="n">
-        <v>137.92</v>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-9</t>
-        </is>
+      <c r="BK8" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="BM8" t="n">
+        <v>135.22</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-5.072385572348653</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-7.681139333748945</t>
+          <t>-5.704721879410656</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
+          <t>-9.182571568251674</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BR8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>-10.82</t>
-        </is>
-      </c>
       <c r="BU8" t="inlineStr">
         <is>
+          <t>-10.55</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
+          <t>16.95</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV8" t="inlineStr">
+      <c r="CW8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4317,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,455 +4372,460 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-11.14</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-9.87</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-5.07</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/04/18</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2024-05-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>42.11</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>-5.02</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-27.32</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-8.53</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/04/18</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>68.42</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>77.96</t>
-        </is>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>-1.24</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>17.15</t>
-        </is>
-      </c>
-      <c r="AY9" t="n">
-        <v>17.57</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>18.67</t>
-        </is>
+        <v>17.47</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>18.39</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>7.66</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
+          <t>18.64</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
         <v>-0.41</v>
       </c>
-      <c r="BD9" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BE9" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="BF9" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>-114.10</t>
-        </is>
-      </c>
       <c r="BG9" t="inlineStr">
         <is>
+          <t>-113.88</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>107.6</t>
-        </is>
-      </c>
-      <c r="BL9" t="n">
-        <v>143.02</v>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-29</t>
-        </is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="BM9" t="n">
+        <v>137.92</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-4.598066706639509</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-5.261909736825444</t>
+          <t>-5.072385572348653</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>-7.681139333748945</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>-9.50</t>
-        </is>
-      </c>
       <c r="BU9" t="inlineStr">
         <is>
+          <t>-10.82</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4799,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.65</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,300 +5014,305 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2024-05-17 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>65.82</t>
-        </is>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.58</v>
+          <t>68.42</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>77.96</t>
+        </is>
       </c>
       <c r="AU10" t="n">
-        <v>-3.24</v>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>-4.46</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-2.39</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>17.08</t>
-        </is>
-      </c>
-      <c r="AY10" t="n">
-        <v>17.65</v>
+          <t>-1.24</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>17.15</t>
+        </is>
       </c>
       <c r="AZ10" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
+        <v>17.57</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>18.43</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-0.43</v>
+          <t>18.67</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>7.66</t>
+        </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="BE10" t="inlineStr">
+        <v>-0.41</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="BF10" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
       <c r="BG10" t="inlineStr">
         <is>
+          <t>-114.10</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
           <t>2025/12/08</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="n">
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="n">
         <v>78.2</v>
       </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>101.1</t>
-        </is>
-      </c>
-      <c r="BL10" t="n">
-        <v>146.34</v>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-22</t>
-        </is>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>107.6</t>
+        </is>
+      </c>
+      <c r="BM10" t="n">
+        <v>143.02</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-4.47736797387843</t>
+          <t>-29</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-5.046513536333805</t>
+          <t>-4.598066706639509</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>-5.261909736825444</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>2025/09/30</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>-8.44</t>
-        </is>
-      </c>
       <c r="BU10" t="inlineStr">
         <is>
+          <t>-9.50</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>正能量智能</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>運動休閒</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-4.914704939634603</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>3.89524476612966</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>0.4035023817520423</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>4.93</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CI10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
           <t>30.08%</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>-1.36%</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
           <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>正能量智能-運動休閒-上櫃</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
+          <t>17.15</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5271,7 +5321,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5281,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,455 +5346,460 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>17.35</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-22.65</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-7.47</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-5.07</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/04/18</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2024-05-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>89.47</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>65.82</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>-4.46</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>17.08</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>18.69</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-114.37</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="BK11" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>101.1</t>
+        </is>
+      </c>
+      <c r="BM11" t="n">
+        <v>146.34</v>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-22</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-4.47736797387843</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-5.046513536333805</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>-8.44</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>-4.914704939634603</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>3.89524476612966</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>0.4035023817520423</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>30.08%</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>-1.36%</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>14.99</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>正能量智能-運動休閒-上櫃</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>運動休閒平上櫃</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-19.78</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-6.93</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/04/18</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>5.12</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>46.67</t>
-        </is>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-4.56</v>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>-4.28</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
-      </c>
-      <c r="AY11" t="n">
-        <v>17.72</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>18.51</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>18.71</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-2.90</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>-114.54</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>92.5</t>
-        </is>
-      </c>
-      <c r="BL11" t="n">
-        <v>146.54</v>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-18</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-4.373886962522906</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-6.701429195048107</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>-7.92</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>-4.914704939634603</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>3.89524476612966</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0.4035023817520423</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>30.08%</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
-        <is>
-          <t>-1.36%</t>
-        </is>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>正能量智能-運動休閒-上櫃</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>運動休閒平上櫃</t>
-        </is>
-      </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
+          <t>17.35</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV11" t="inlineStr">
+      <c r="CW11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5763,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,455 +5833,460 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-19.78</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-04-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>19.65</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-6.93</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-5.07</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2025/04/18</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2024-05-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>15.56</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>5.12</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>46.67</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>-4.28</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>16.91</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>18.71</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-2.90</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-114.54</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>1705.787965616046</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="BK12" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="BM12" t="n">
+        <v>146.54</v>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-18</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-4.373886962522906</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-6.701429195048107</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>-7.92</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>正能量智能</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>運動休閒</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>-4.914704939634603</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>3.89524476612966</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>0.4035023817520423</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>30.08%</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>-1.36%</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>14.99</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>正能量智能-運動休閒-上櫃</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>運動休閒平上櫃</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-8.21</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-04-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>24.6</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-9.87</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/04/18</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/10/28</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>29.33</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-5.42</v>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>-4.16</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>16.81</t>
-        </is>
-      </c>
-      <c r="AY12" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>18.73</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-15.72</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>-114.44</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>1708.078192252511</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BJ12" t="n">
-        <v>95</v>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="BL12" t="n">
-        <v>146.98</v>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-3.950697465700142</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-10.64768623624541</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>-10.82</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>正能量智能</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>運動休閒</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>-4.914704939634603</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>3.89524476612966</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>0.4035023817520423</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI12" t="inlineStr">
-        <is>
-          <t>30.08%</t>
-        </is>
-      </c>
-      <c r="CJ12" t="inlineStr">
-        <is>
-          <t>-1.36%</t>
-        </is>
-      </c>
-      <c r="CK12" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
-      <c r="CL12" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="CM12" t="inlineStr">
-        <is>
-          <t>運動產品63.00%、GPS27.00%、MMDS降頻器及雙向收發機9.00%、商品- 其他1.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN12" t="inlineStr">
-        <is>
-          <t>正能量智能-運動休閒-上櫃</t>
-        </is>
-      </c>
-      <c r="CO12" t="inlineStr">
-        <is>
-          <t>運動休閒平上櫃</t>
-        </is>
-      </c>
-      <c r="CP12" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="CQ12" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CU12" t="inlineStr">
+        <is>
           <t>8.32</t>
         </is>
       </c>
-      <c r="CU12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 裝置/器材零組件、軟體開發、運動用品、穿戴式裝置、通訊服務、數位內容、運動服務/顧問、運動行銷/媒體</t>
         </is>
       </c>
-      <c r="CV12" t="inlineStr">
+      <c r="CW12" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Result/checksun_type/運動行銷_媒體.xlsx
+++ b/Result/checksun_type/運動行銷_媒體.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,51 +1159,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>78.85</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.1</v>
+        <v>2.81</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AZ2" t="n">
         <v>17.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>18.12</v>
+        <v>18.1</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>32.10</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.33</v>
+        <v>-0.3</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-110.52</t>
+          <t>-109.39</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>1705.787965616046</t>
+          <t>1703.712446351931</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>122.2</v>
+        <v>116</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>108.8</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>121.68</v>
+        <v>115.38</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1.114073367590853</t>
+          <t>0.2113547068118805</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>3.357272155797403</t>
+          <t>7.501209116026914</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>264</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>78.85</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AV3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>-5.42</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>17.31</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>18.47</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>32.10</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
         <v>-0.23</v>
       </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17.15</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>18.49</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>23.92</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="BE3" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-111.37</t>
+          <t>-110.52</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>1705.787965616046</t>
+          <t>1703.712446351931</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>131.4</v>
+        <v>122.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>121.78</v>
+        <v>121.68</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1.927045280934172</t>
+          <t>-1.114073367590853</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>7.710316778476752</t>
+          <t>3.357272155797403</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>264</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4